--- a/example/reports/dmz_firewall-review.xlsx
+++ b/example/reports/dmz_firewall-review.xlsx
@@ -70,7 +70,7 @@
     <t>Backup timestamp</t>
   </si>
   <si>
-    <t>2026-07-30 18:33</t>
+    <t>2026-07-30 19:26</t>
   </si>
   <si>
     <t>Report generated</t>

--- a/example/reports/dmz_firewall-review.xlsx
+++ b/example/reports/dmz_firewall-review.xlsx
@@ -70,7 +70,7 @@
     <t>Backup timestamp</t>
   </si>
   <si>
-    <t>2026-07-30 19:26</t>
+    <t>2026-08-04 22:41</t>
   </si>
   <si>
     <t>Report generated</t>
@@ -640,7 +640,7 @@
     <t>Past its stated expiry date</t>
   </si>
   <si>
-    <t>The description gives an expiry of 2026-06-13, 47 days ago, but the rule is still active.</t>
+    <t>The description gives an expiry of 2026-06-13, 52 days ago, but the rule is still active.</t>
   </si>
   <si>
     <t>Remove the rule, or extend it with a new change reference.</t>
@@ -697,7 +697,7 @@
     <t>Expires soon</t>
   </si>
   <si>
-    <t>The stated expiry is 2026-08-27, in 28 days.</t>
+    <t>The stated expiry is 2026-08-27, in 23 days.</t>
   </si>
   <si>
     <t>Confirm whether the access is still needed before it lapses.</t>

--- a/example/reports/dmz_firewall-review.xlsx
+++ b/example/reports/dmz_firewall-review.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="305">
   <si>
     <t>Firewall Rule Review</t>
   </si>
@@ -70,12 +70,15 @@
     <t>Backup timestamp</t>
   </si>
   <si>
-    <t>2026-08-04 22:41</t>
+    <t>2026-08-05 00:22</t>
   </si>
   <si>
     <t>Report generated</t>
   </si>
   <si>
+    <t>2026-08-05 00:23</t>
+  </si>
+  <si>
     <t>Tool version</t>
   </si>
   <si>
@@ -175,18 +178,18 @@
     <t>Status</t>
   </si>
   <si>
+    <t>Peer (other side)</t>
+  </si>
+  <si>
+    <t>Peer addresses</t>
+  </si>
+  <si>
     <t>Your networks</t>
   </si>
   <si>
     <t>Your networks (addresses)</t>
   </si>
   <si>
-    <t>Peer (other side)</t>
-  </si>
-  <si>
-    <t>Peer addresses</t>
-  </si>
-  <si>
     <t>Peer team</t>
   </si>
   <si>
@@ -238,15 +241,15 @@
     <t>allow</t>
   </si>
   <si>
+    <t>any</t>
+  </si>
+  <si>
     <t>dmz-host-01</t>
   </si>
   <si>
     <t>172.16.0.0/16</t>
   </si>
   <si>
-    <t>any</t>
-  </si>
-  <si>
     <t>tcp/443</t>
   </si>
   <si>
@@ -640,7 +643,7 @@
     <t>Past its stated expiry date</t>
   </si>
   <si>
-    <t>The description gives an expiry of 2026-06-13, 52 days ago, but the rule is still active.</t>
+    <t>The description gives an expiry of 2026-06-13, 53 days ago, but the rule is still active.</t>
   </si>
   <si>
     <t>Remove the rule, or extend it with a new change reference.</t>
@@ -697,7 +700,7 @@
     <t>Expires soon</t>
   </si>
   <si>
-    <t>The stated expiry is 2026-08-27, in 23 days.</t>
+    <t>The stated expiry is 2026-08-27, in 22 days.</t>
   </si>
   <si>
     <t>Confirm whether the access is still needed before it lapses.</t>
@@ -1485,20 +1488,20 @@
         <v>14</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B14" s="4">
         <v>20</v>
@@ -1506,7 +1509,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15" s="4">
         <v>3</v>
@@ -1514,7 +1517,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B16" s="4">
         <v>10</v>
@@ -1522,7 +1525,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B17" s="4">
         <v>7</v>
@@ -1530,7 +1533,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B18" s="4">
         <v>0</v>
@@ -1538,7 +1541,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B19" s="4">
         <v>10</v>
@@ -1546,7 +1549,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B20" s="4">
         <v>18</v>
@@ -1554,20 +1557,20 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="B24" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1575,27 +1578,27 @@
     </row>
     <row r="26" spans="1:2">
       <c r="B26" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="B27" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="B28" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="B29" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="B30" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1603,7 +1606,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="B32" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1611,7 +1614,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="B34" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1619,7 +1622,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="B36" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1627,22 +1630,22 @@
     </row>
     <row r="38" spans="1:2">
       <c r="B38" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="B39" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="B42" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1663,8 +1666,8 @@
     <col min="6" max="6" width="34.7109375" customWidth="1"/>
     <col min="7" max="7" width="22.7109375" customWidth="1"/>
     <col min="8" max="8" width="10.7109375" customWidth="1"/>
-    <col min="9" max="10" width="30.7109375" customWidth="1"/>
-    <col min="11" max="12" width="38.7109375" customWidth="1"/>
+    <col min="9" max="10" width="38.7109375" customWidth="1"/>
+    <col min="11" max="12" width="30.7109375" customWidth="1"/>
     <col min="13" max="13" width="16.7109375" customWidth="1"/>
     <col min="14" max="15" width="26.7109375" customWidth="1"/>
     <col min="16" max="16" width="24.7109375" customWidth="1"/>
@@ -1679,101 +1682,101 @@
   <sheetData>
     <row r="1" spans="1:24" ht="30" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q1" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R1" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="S1" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T1" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="U1" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="V1" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="W1" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="X1" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:24">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D2" s="8">
         <v>2</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J2" s="8" t="s">
         <v>70</v>
@@ -1782,64 +1785,64 @@
         <v>71</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M2" s="8"/>
       <c r="N2" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="O2" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="O2" s="8" t="s">
-        <v>69</v>
-      </c>
       <c r="P2" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q2" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R2" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="S2" s="8" t="s">
         <v>5</v>
       </c>
       <c r="T2" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U2" s="8"/>
       <c r="V2" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W2" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X2" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:24">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D3" s="8">
         <v>13</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J3" s="8" t="s">
         <v>70</v>
@@ -1848,62 +1851,62 @@
         <v>71</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M3" s="8"/>
       <c r="N3" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="O3" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="O3" s="8" t="s">
-        <v>69</v>
-      </c>
       <c r="P3" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R3" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S3" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="T3" s="8"/>
       <c r="U3" s="8"/>
       <c r="V3" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W3" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X3" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:24">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D4" s="8">
         <v>2</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J4" s="8" t="s">
         <v>70</v>
@@ -1912,39 +1915,39 @@
         <v>71</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M4" s="8"/>
       <c r="N4" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="O4" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="O4" s="8" t="s">
-        <v>69</v>
-      </c>
       <c r="P4" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="S4" s="8" t="s">
         <v>5</v>
       </c>
       <c r="T4" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U4" s="8"/>
       <c r="V4" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W4" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X4" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1991,337 +1994,337 @@
   <sheetData>
     <row r="1" spans="1:24" ht="30" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J1" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="L1" s="6" t="s">
-        <v>51</v>
-      </c>
       <c r="M1" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q1" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R1" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="S1" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T1" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="U1" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="V1" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="W1" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="X1" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:24">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D2" s="8">
         <v>3</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M2" s="8"/>
       <c r="N2" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O2" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P2" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q2" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="R2" s="8" t="s">
         <v>5</v>
       </c>
       <c r="S2" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="T2" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="U2" s="8"/>
       <c r="V2" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W2" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="X2" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:24">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D3" s="8">
         <v>5</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K3" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="N3" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="O3" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="M3" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="N3" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="O3" s="8" t="s">
-        <v>95</v>
-      </c>
       <c r="P3" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="R3" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S3" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="T3" s="8"/>
       <c r="U3" s="8"/>
       <c r="V3" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W3" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="X3" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:24">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D4" s="8">
         <v>8</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M4" s="8"/>
       <c r="N4" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="S4" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T4" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="U4" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V4" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W4" s="12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="X4" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:24">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D5" s="8">
         <v>9</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M5" s="8"/>
       <c r="N5" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P5" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q5" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R5" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S5" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="T5" s="8"/>
       <c r="U5" s="8"/>
       <c r="V5" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W5" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="X5" s="8"/>
     </row>
@@ -2329,401 +2332,401 @@
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D6" s="14">
         <v>10</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M6" s="14"/>
       <c r="N6" s="14" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O6" s="14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P6" s="14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q6" s="14" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="R6" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="S6" s="14" t="s">
         <v>5</v>
       </c>
       <c r="T6" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="U6" s="14"/>
       <c r="V6" s="14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W6" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="X6" s="14" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:24">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D7" s="8">
         <v>11</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K7" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="N7" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="L7" s="8" t="s">
+      <c r="O7" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="M7" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="N7" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="O7" s="8" t="s">
-        <v>127</v>
-      </c>
       <c r="P7" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q7" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R7" s="8" t="s">
         <v>5</v>
       </c>
       <c r="S7" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="T7" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="U7" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="V7" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W7" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="X7" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:24">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D8" s="8">
         <v>14</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M8" s="8"/>
       <c r="N8" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O8" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P8" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q8" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="R8" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="S8" s="8" t="s">
         <v>5</v>
       </c>
       <c r="T8" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="U8" s="8"/>
       <c r="V8" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W8" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="X8" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:24">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D9" s="8">
         <v>16</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K9" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="N9" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="L9" s="8" t="s">
+      <c r="O9" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="M9" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="N9" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="O9" s="8" t="s">
-        <v>95</v>
-      </c>
       <c r="P9" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q9" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="R9" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="S9" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T9" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="U9" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="V9" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W9" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="X9" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10" spans="1:24">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D10" s="8">
         <v>19</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M10" s="8"/>
       <c r="N10" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O10" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P10" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q10" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R10" s="8" t="s">
         <v>5</v>
       </c>
       <c r="S10" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="T10" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="U10" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V10" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W10" s="12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="X10" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:24">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D11" s="8">
         <v>20</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M11" s="8"/>
       <c r="N11" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O11" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P11" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q11" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R11" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="S11" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T11" s="8"/>
       <c r="U11" s="8"/>
       <c r="V11" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W11" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="X11" s="8"/>
     </row>
@@ -2776,536 +2779,536 @@
   <sheetData>
     <row r="1" spans="1:24" ht="30" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J1" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="L1" s="6" t="s">
-        <v>51</v>
-      </c>
       <c r="M1" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q1" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R1" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="S1" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T1" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="U1" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="V1" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="W1" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="X1" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:24">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D2" s="8">
         <v>1</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M2" s="8"/>
       <c r="N2" s="8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O2" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P2" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q2" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="R2" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S2" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="T2" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="U2" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="V2" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W2" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="X2" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:24">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D3" s="8">
         <v>6</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M3" s="8"/>
       <c r="N3" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P3" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R3" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="S3" s="8" t="s">
         <v>5</v>
       </c>
       <c r="T3" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="U3" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="V3" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W3" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="X3" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="4" spans="1:24">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D4" s="8">
         <v>7</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M4" s="8"/>
       <c r="N4" s="8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="R4" s="8" t="s">
         <v>5</v>
       </c>
       <c r="S4" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="T4" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="U4" s="8"/>
       <c r="V4" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W4" s="8"/>
       <c r="X4" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:24">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D5" s="8">
         <v>12</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M5" s="8"/>
       <c r="N5" s="8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P5" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q5" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="R5" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="S5" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T5" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="U5" s="8"/>
       <c r="V5" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W5" s="8"/>
       <c r="X5" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:24">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D6" s="8">
         <v>17</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M6" s="8"/>
       <c r="N6" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P6" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q6" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R6" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S6" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="T6" s="8"/>
       <c r="U6" s="8"/>
       <c r="V6" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W6" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="X6" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:24">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D7" s="8">
         <v>18</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M7" s="8"/>
       <c r="N7" s="8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O7" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P7" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q7" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="R7" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="S7" s="8" t="s">
         <v>5</v>
       </c>
       <c r="T7" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="U7" s="8"/>
       <c r="V7" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W7" s="8"/>
       <c r="X7" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8" spans="1:24">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D8" s="8">
         <v>1</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M8" s="8"/>
       <c r="N8" s="8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O8" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P8" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q8" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="R8" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S8" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="T8" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="U8" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="V8" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W8" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="X8" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -3356,696 +3359,696 @@
   <sheetData>
     <row r="1" spans="1:24" ht="30" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J1" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="L1" s="6" t="s">
-        <v>51</v>
-      </c>
       <c r="M1" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q1" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R1" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="S1" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T1" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="U1" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="V1" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="W1" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="X1" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:24">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D2" s="8">
         <v>4</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J2" s="8"/>
       <c r="K2" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M2" s="8"/>
       <c r="N2" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O2" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P2" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q2" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R2" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="S2" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T2" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U2" s="8"/>
       <c r="V2" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W2" s="8"/>
       <c r="X2" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:24">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D3" s="8">
         <v>15</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J3" s="8"/>
       <c r="K3" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M3" s="8"/>
       <c r="N3" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P3" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R3" s="8" t="s">
         <v>5</v>
       </c>
       <c r="S3" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="T3" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="U3" s="8"/>
       <c r="V3" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W3" s="8"/>
       <c r="X3" s="8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:24">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D4" s="8">
         <v>4</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J4" s="8"/>
       <c r="K4" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M4" s="8"/>
       <c r="N4" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="S4" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T4" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U4" s="8"/>
       <c r="V4" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W4" s="8"/>
       <c r="X4" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:24">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D5" s="8">
         <v>15</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F5" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="G5" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="G5" s="8" t="s">
-        <v>181</v>
-      </c>
       <c r="H5" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J5" s="8"/>
       <c r="K5" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M5" s="8"/>
       <c r="N5" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P5" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q5" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R5" s="8" t="s">
         <v>5</v>
       </c>
       <c r="S5" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="T5" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="U5" s="8"/>
       <c r="V5" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W5" s="8"/>
       <c r="X5" s="8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:24">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D6" s="8">
         <v>4</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J6" s="8"/>
       <c r="K6" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M6" s="8"/>
       <c r="N6" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P6" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q6" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R6" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="S6" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T6" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U6" s="8"/>
       <c r="V6" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W6" s="8"/>
       <c r="X6" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7" spans="1:24">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D7" s="8">
         <v>15</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F7" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="G7" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="G7" s="8" t="s">
-        <v>185</v>
-      </c>
       <c r="H7" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J7" s="8"/>
       <c r="K7" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M7" s="8"/>
       <c r="N7" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O7" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P7" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q7" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R7" s="8" t="s">
         <v>5</v>
       </c>
       <c r="S7" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="T7" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="U7" s="8"/>
       <c r="V7" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W7" s="8"/>
       <c r="X7" s="8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8" spans="1:24">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D8" s="8">
         <v>4</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J8" s="8"/>
       <c r="K8" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M8" s="8"/>
       <c r="N8" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O8" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P8" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q8" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R8" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="S8" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T8" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U8" s="8"/>
       <c r="V8" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W8" s="8"/>
       <c r="X8" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="9" spans="1:24">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D9" s="8">
         <v>15</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F9" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="G9" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="G9" s="8" t="s">
-        <v>189</v>
-      </c>
       <c r="H9" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J9" s="8"/>
       <c r="K9" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M9" s="8"/>
       <c r="N9" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O9" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P9" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q9" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R9" s="8" t="s">
         <v>5</v>
       </c>
       <c r="S9" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="T9" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="U9" s="8"/>
       <c r="V9" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W9" s="8"/>
       <c r="X9" s="8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10" spans="1:24">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D10" s="8">
         <v>4</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J10" s="8"/>
       <c r="K10" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M10" s="8"/>
       <c r="N10" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O10" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P10" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q10" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R10" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="S10" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T10" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U10" s="8"/>
       <c r="V10" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W10" s="8"/>
       <c r="X10" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11" spans="1:24">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D11" s="8">
         <v>15</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F11" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="G11" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="G11" s="8" t="s">
-        <v>193</v>
-      </c>
       <c r="H11" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J11" s="8"/>
       <c r="K11" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M11" s="8"/>
       <c r="N11" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O11" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P11" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q11" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R11" s="8" t="s">
         <v>5</v>
       </c>
       <c r="S11" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="T11" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="U11" s="8"/>
       <c r="V11" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W11" s="8"/>
       <c r="X11" s="8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -4082,439 +4085,439 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>
@@ -4535,24 +4538,24 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C2" s="8">
         <v>3</v>
@@ -4581,427 +4584,427 @@
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F2" s="8"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F4" s="8"/>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="8" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F6" s="8"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F8" s="8"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F9" s="8"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F10" s="8"/>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F12" s="8"/>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F13" s="8"/>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F14" s="8"/>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F16" s="8"/>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F17" s="8"/>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F18" s="8"/>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F20" s="8"/>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F21" s="8"/>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F22" s="8"/>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F23" s="8"/>
     </row>

--- a/example/reports/dmz_firewall-review.xlsx
+++ b/example/reports/dmz_firewall-review.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="304">
   <si>
     <t>Firewall Rule Review</t>
   </si>
@@ -70,15 +70,12 @@
     <t>Backup timestamp</t>
   </si>
   <si>
-    <t>2026-08-05 00:22</t>
+    <t>2026-08-07 16:09</t>
   </si>
   <si>
     <t>Report generated</t>
   </si>
   <si>
-    <t>2026-08-05 00:23</t>
-  </si>
-  <si>
     <t>Tool version</t>
   </si>
   <si>
@@ -643,7 +640,7 @@
     <t>Past its stated expiry date</t>
   </si>
   <si>
-    <t>The description gives an expiry of 2026-06-13, 53 days ago, but the rule is still active.</t>
+    <t>The description gives an expiry of 2026-06-13, 55 days ago, but the rule is still active.</t>
   </si>
   <si>
     <t>Remove the rule, or extend it with a new change reference.</t>
@@ -700,7 +697,7 @@
     <t>Expires soon</t>
   </si>
   <si>
-    <t>The stated expiry is 2026-08-27, in 22 days.</t>
+    <t>The stated expiry is 2026-08-27, in 20 days.</t>
   </si>
   <si>
     <t>Confirm whether the access is still needed before it lapses.</t>
@@ -1488,20 +1485,20 @@
         <v>14</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" s="4">
         <v>20</v>
@@ -1509,7 +1506,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" s="4">
         <v>3</v>
@@ -1517,7 +1514,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" s="4">
         <v>10</v>
@@ -1525,7 +1522,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B17" s="4">
         <v>7</v>
@@ -1533,7 +1530,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B18" s="4">
         <v>0</v>
@@ -1541,7 +1538,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B19" s="4">
         <v>10</v>
@@ -1549,7 +1546,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B20" s="4">
         <v>18</v>
@@ -1557,20 +1554,20 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="B24" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1578,27 +1575,27 @@
     </row>
     <row r="26" spans="1:2">
       <c r="B26" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="B27" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="B28" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="B29" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="B30" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1606,7 +1603,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="B32" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1614,7 +1611,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="B34" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1622,7 +1619,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="B36" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1630,22 +1627,22 @@
     </row>
     <row r="38" spans="1:2">
       <c r="B38" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="B39" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="B42" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1682,272 +1679,272 @@
   <sheetData>
     <row r="1" spans="1:24" ht="30" customHeight="1">
       <c r="A1" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="R1" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="S1" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="V1" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="W1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="X1" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="X1" s="6" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:24">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D2" s="8">
         <v>2</v>
       </c>
       <c r="E2" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="H2" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="H2" s="8" t="s">
-        <v>69</v>
-      </c>
       <c r="I2" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K2" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="K2" s="8" t="s">
+      <c r="L2" s="8" t="s">
         <v>71</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>72</v>
       </c>
       <c r="M2" s="8"/>
       <c r="N2" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="O2" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="O2" s="8" t="s">
-        <v>71</v>
-      </c>
       <c r="P2" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q2" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="Q2" s="8" t="s">
+      <c r="R2" s="8" t="s">
         <v>74</v>
-      </c>
-      <c r="R2" s="8" t="s">
-        <v>75</v>
       </c>
       <c r="S2" s="8" t="s">
         <v>5</v>
       </c>
       <c r="T2" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="U2" s="8"/>
       <c r="V2" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W2" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="X2" s="8" t="s">
         <v>77</v>
-      </c>
-      <c r="X2" s="8" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:24">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D3" s="8">
         <v>13</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G3" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H3" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="H3" s="8" t="s">
-        <v>69</v>
-      </c>
       <c r="I3" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K3" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="J3" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="K3" s="8" t="s">
+      <c r="L3" s="8" t="s">
         <v>71</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>72</v>
       </c>
       <c r="M3" s="8"/>
       <c r="N3" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="O3" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="O3" s="8" t="s">
-        <v>71</v>
-      </c>
       <c r="P3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q3" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="Q3" s="8" t="s">
+      <c r="R3" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="S3" s="8" t="s">
         <v>74</v>
-      </c>
-      <c r="R3" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="S3" s="8" t="s">
-        <v>75</v>
       </c>
       <c r="T3" s="8"/>
       <c r="U3" s="8"/>
       <c r="V3" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W3" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="X3" s="8" t="s">
         <v>81</v>
-      </c>
-      <c r="X3" s="8" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:24">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D4" s="8">
         <v>2</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F4" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="G4" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="G4" s="8" t="s">
-        <v>85</v>
-      </c>
       <c r="H4" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I4" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K4" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="J4" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="K4" s="8" t="s">
+      <c r="L4" s="8" t="s">
         <v>71</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>72</v>
       </c>
       <c r="M4" s="8"/>
       <c r="N4" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="O4" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="O4" s="8" t="s">
-        <v>71</v>
-      </c>
       <c r="P4" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q4" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="Q4" s="8" t="s">
+      <c r="R4" s="8" t="s">
         <v>74</v>
-      </c>
-      <c r="R4" s="8" t="s">
-        <v>75</v>
       </c>
       <c r="S4" s="8" t="s">
         <v>5</v>
       </c>
       <c r="T4" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="U4" s="8"/>
       <c r="V4" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W4" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="X4" s="8" t="s">
         <v>77</v>
-      </c>
-      <c r="X4" s="8" t="s">
-        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1994,337 +1991,337 @@
   <sheetData>
     <row r="1" spans="1:24" ht="30" customHeight="1">
       <c r="A1" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="I1" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="J1" s="6" t="s">
+      <c r="L1" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="M1" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="K1" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="R1" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="S1" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="V1" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="W1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="X1" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="X1" s="6" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:24">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D2" s="8">
         <v>3</v>
       </c>
       <c r="E2" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I2" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="G2" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>88</v>
-      </c>
       <c r="J2" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M2" s="8"/>
       <c r="N2" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="P2" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q2" s="8" t="s">
         <v>88</v>
-      </c>
-      <c r="O2" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="P2" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q2" s="8" t="s">
-        <v>89</v>
       </c>
       <c r="R2" s="8" t="s">
         <v>5</v>
       </c>
       <c r="S2" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="T2" s="9" t="s">
         <v>90</v>
-      </c>
-      <c r="T2" s="9" t="s">
-        <v>91</v>
       </c>
       <c r="U2" s="8"/>
       <c r="V2" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W2" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="X2" s="8" t="s">
         <v>92</v>
-      </c>
-      <c r="X2" s="8" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:24">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D3" s="8">
         <v>5</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F3" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I3" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="G3" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="I3" s="8" t="s">
+      <c r="J3" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="K3" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="J3" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="K3" s="8" t="s">
+      <c r="L3" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="M3" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="N3" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="O3" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="P3" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="N3" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="O3" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="P3" s="8" t="s">
+      <c r="Q3" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="Q3" s="8" t="s">
-        <v>100</v>
-      </c>
       <c r="R3" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S3" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="T3" s="8"/>
       <c r="U3" s="8"/>
       <c r="V3" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W3" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="X3" s="8" t="s">
         <v>101</v>
-      </c>
-      <c r="X3" s="8" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:24">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D4" s="8">
         <v>8</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F4" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="K4" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="G4" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="K4" s="8" t="s">
+      <c r="L4" s="8" t="s">
         <v>104</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>105</v>
       </c>
       <c r="M4" s="8"/>
       <c r="N4" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P4" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q4" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="Q4" s="8" t="s">
+      <c r="R4" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="S4" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="T4" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="R4" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="S4" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="T4" s="9" t="s">
+      <c r="U4" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="U4" s="8" t="s">
+      <c r="V4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="W4" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="V4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="W4" s="12" t="s">
+      <c r="X4" s="8" t="s">
         <v>110</v>
-      </c>
-      <c r="X4" s="8" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:24">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D5" s="8">
         <v>9</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F5" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I5" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="G5" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="I5" s="8" t="s">
+      <c r="J5" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="K5" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="J5" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="K5" s="8" t="s">
+      <c r="L5" s="8" t="s">
         <v>114</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>115</v>
       </c>
       <c r="M5" s="8"/>
       <c r="N5" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="O5" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="O5" s="8" t="s">
-        <v>114</v>
-      </c>
       <c r="P5" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q5" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R5" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S5" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="T5" s="8"/>
       <c r="U5" s="8"/>
       <c r="V5" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W5" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="X5" s="8"/>
     </row>
@@ -2332,401 +2329,401 @@
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D6" s="14">
         <v>10</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F6" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="H6" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="G6" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="H6" s="14" t="s">
+      <c r="I6" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="K6" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="I6" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="J6" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="K6" s="14" t="s">
+      <c r="L6" s="14" t="s">
         <v>120</v>
-      </c>
-      <c r="L6" s="14" t="s">
-        <v>121</v>
       </c>
       <c r="M6" s="14"/>
       <c r="N6" s="14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O6" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P6" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q6" s="14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="R6" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="S6" s="14" t="s">
         <v>5</v>
       </c>
       <c r="T6" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="U6" s="14"/>
       <c r="V6" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W6" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="X6" s="14" t="s">
         <v>124</v>
-      </c>
-      <c r="X6" s="14" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:24">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D7" s="8">
         <v>11</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F7" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I7" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="G7" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="I7" s="8" t="s">
+      <c r="J7" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="K7" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="J7" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="K7" s="8" t="s">
+      <c r="L7" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="L7" s="8" t="s">
-        <v>129</v>
-      </c>
       <c r="M7" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="N7" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="O7" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="O7" s="8" t="s">
-        <v>128</v>
-      </c>
       <c r="P7" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q7" s="8" t="s">
         <v>106</v>
-      </c>
-      <c r="Q7" s="8" t="s">
-        <v>107</v>
       </c>
       <c r="R7" s="8" t="s">
         <v>5</v>
       </c>
       <c r="S7" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="T7" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="U7" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="U7" s="8" t="s">
+      <c r="V7" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="W7" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="V7" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="W7" s="11" t="s">
+      <c r="X7" s="8" t="s">
         <v>132</v>
-      </c>
-      <c r="X7" s="8" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:24">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D8" s="8">
         <v>14</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G8" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H8" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="H8" s="8" t="s">
-        <v>69</v>
-      </c>
       <c r="I8" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M8" s="8"/>
       <c r="N8" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="O8" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="P8" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q8" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="O8" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="P8" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q8" s="8" t="s">
-        <v>89</v>
-      </c>
       <c r="R8" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="S8" s="8" t="s">
         <v>5</v>
       </c>
       <c r="T8" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U8" s="8"/>
       <c r="V8" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W8" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="X8" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:24">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D9" s="8">
         <v>16</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F9" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="O9" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="P9" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q9" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="R9" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="S9" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="T9" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="G9" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="M9" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="N9" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="O9" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="P9" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q9" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="R9" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="S9" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="T9" s="9" t="s">
+      <c r="U9" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="V9" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="W9" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="X9" s="8" t="s">
         <v>138</v>
-      </c>
-      <c r="U9" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="V9" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="W9" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="X9" s="8" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="10" spans="1:24">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D10" s="8">
         <v>19</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G10" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="H10" s="8" t="s">
-        <v>69</v>
-      </c>
       <c r="I10" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K10" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="L10" s="8" t="s">
         <v>104</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>105</v>
       </c>
       <c r="M10" s="8"/>
       <c r="N10" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O10" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P10" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q10" s="8" t="s">
         <v>106</v>
-      </c>
-      <c r="Q10" s="8" t="s">
-        <v>107</v>
       </c>
       <c r="R10" s="8" t="s">
         <v>5</v>
       </c>
       <c r="S10" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="T10" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="U10" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="V10" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="W10" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="X10" s="8" t="s">
         <v>141</v>
-      </c>
-      <c r="U10" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="V10" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="W10" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="X10" s="8" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:24">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D11" s="8">
         <v>20</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G11" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="H11" s="8" t="s">
-        <v>69</v>
-      </c>
       <c r="I11" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="K11" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="J11" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="K11" s="8" t="s">
+      <c r="L11" s="8" t="s">
         <v>114</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>115</v>
       </c>
       <c r="M11" s="8"/>
       <c r="N11" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="O11" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="O11" s="8" t="s">
-        <v>114</v>
-      </c>
       <c r="P11" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q11" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R11" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="S11" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T11" s="8"/>
       <c r="U11" s="8"/>
       <c r="V11" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W11" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="X11" s="8"/>
     </row>
@@ -2779,536 +2776,536 @@
   <sheetData>
     <row r="1" spans="1:24" ht="30" customHeight="1">
       <c r="A1" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="I1" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="J1" s="6" t="s">
+      <c r="L1" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="M1" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="K1" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="R1" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="S1" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="V1" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="W1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="X1" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="X1" s="6" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:24">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D2" s="8">
         <v>1</v>
       </c>
       <c r="E2" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I2" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="G2" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="I2" s="8" t="s">
+      <c r="J2" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="L2" s="8" t="s">
         <v>146</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>147</v>
       </c>
       <c r="M2" s="8"/>
       <c r="N2" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O2" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P2" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q2" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="R2" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="S2" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="T2" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="R2" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="S2" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="T2" s="9" t="s">
+      <c r="U2" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="V2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="W2" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="X2" s="8" t="s">
         <v>149</v>
-      </c>
-      <c r="U2" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="V2" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="W2" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="X2" s="8" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:24">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D3" s="8">
         <v>6</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F3" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I3" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="G3" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="I3" s="8" t="s">
+      <c r="J3" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="L3" s="8" t="s">
         <v>152</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>153</v>
       </c>
       <c r="M3" s="8"/>
       <c r="N3" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="O3" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="P3" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="O3" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="P3" s="8" t="s">
-        <v>155</v>
-      </c>
       <c r="Q3" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R3" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="S3" s="8" t="s">
         <v>5</v>
       </c>
       <c r="T3" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="U3" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="V3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="W3" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="X3" s="8" t="s">
         <v>156</v>
-      </c>
-      <c r="U3" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="V3" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="W3" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="X3" s="8" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="4" spans="1:24">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D4" s="8">
         <v>7</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G4" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H4" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="H4" s="8" t="s">
-        <v>69</v>
-      </c>
       <c r="I4" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="L4" s="8" t="s">
         <v>146</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>147</v>
       </c>
       <c r="M4" s="8"/>
       <c r="N4" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P4" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q4" s="8" t="s">
         <v>159</v>
-      </c>
-      <c r="Q4" s="8" t="s">
-        <v>160</v>
       </c>
       <c r="R4" s="8" t="s">
         <v>5</v>
       </c>
       <c r="S4" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="T4" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="U4" s="8"/>
       <c r="V4" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W4" s="8"/>
       <c r="X4" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" spans="1:24">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D5" s="8">
         <v>12</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G5" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H5" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="H5" s="8" t="s">
-        <v>69</v>
-      </c>
       <c r="I5" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="L5" s="8" t="s">
         <v>146</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>147</v>
       </c>
       <c r="M5" s="8"/>
       <c r="N5" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P5" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q5" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R5" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="S5" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T5" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="U5" s="8"/>
       <c r="V5" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W5" s="8"/>
       <c r="X5" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6" spans="1:24">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D6" s="8">
         <v>17</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G6" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H6" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="H6" s="8" t="s">
-        <v>69</v>
-      </c>
       <c r="I6" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="L6" s="8" t="s">
         <v>152</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>153</v>
       </c>
       <c r="M6" s="8"/>
       <c r="N6" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="O6" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="P6" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="O6" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="P6" s="8" t="s">
-        <v>155</v>
-      </c>
       <c r="Q6" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R6" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S6" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="T6" s="8"/>
       <c r="U6" s="8"/>
       <c r="V6" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W6" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="X6" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:24">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D7" s="8">
         <v>18</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G7" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H7" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="H7" s="8" t="s">
-        <v>69</v>
-      </c>
       <c r="I7" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="L7" s="8" t="s">
         <v>146</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>147</v>
       </c>
       <c r="M7" s="8"/>
       <c r="N7" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O7" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P7" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q7" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="Q7" s="8" t="s">
-        <v>160</v>
-      </c>
       <c r="R7" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="S7" s="8" t="s">
         <v>5</v>
       </c>
       <c r="T7" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="U7" s="8"/>
       <c r="V7" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W7" s="8"/>
       <c r="X7" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:24">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D8" s="8">
         <v>1</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I8" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="L8" s="8" t="s">
         <v>146</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>147</v>
       </c>
       <c r="M8" s="8"/>
       <c r="N8" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O8" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P8" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q8" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="R8" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="S8" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="T8" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="R8" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="S8" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="T8" s="9" t="s">
+      <c r="U8" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="V8" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="W8" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="X8" s="8" t="s">
         <v>149</v>
-      </c>
-      <c r="U8" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="V8" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="W8" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="X8" s="8" t="s">
-        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -3359,696 +3356,696 @@
   <sheetData>
     <row r="1" spans="1:24" ht="30" customHeight="1">
       <c r="A1" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="I1" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="J1" s="6" t="s">
+      <c r="L1" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="M1" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="K1" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="R1" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="S1" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="V1" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="W1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="X1" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="X1" s="6" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:24">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D2" s="8">
         <v>4</v>
       </c>
       <c r="E2" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I2" s="8" t="s">
         <v>173</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>174</v>
       </c>
       <c r="J2" s="8"/>
       <c r="K2" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M2" s="8"/>
       <c r="N2" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O2" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P2" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q2" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R2" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="S2" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T2" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="U2" s="8"/>
       <c r="V2" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W2" s="8"/>
       <c r="X2" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:24">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D3" s="8">
         <v>15</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G3" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H3" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="H3" s="8" t="s">
-        <v>69</v>
-      </c>
       <c r="I3" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J3" s="8"/>
       <c r="K3" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M3" s="8"/>
       <c r="N3" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P3" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R3" s="8" t="s">
         <v>5</v>
       </c>
       <c r="S3" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="T3" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="U3" s="8"/>
       <c r="V3" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W3" s="8"/>
       <c r="X3" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" spans="1:24">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D4" s="8">
         <v>4</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F4" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="G4" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="G4" s="8" t="s">
-        <v>182</v>
-      </c>
       <c r="H4" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J4" s="8"/>
       <c r="K4" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M4" s="8"/>
       <c r="N4" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="S4" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T4" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="U4" s="8"/>
       <c r="V4" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W4" s="8"/>
       <c r="X4" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:24">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D5" s="8">
         <v>15</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J5" s="8"/>
       <c r="K5" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M5" s="8"/>
       <c r="N5" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P5" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q5" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R5" s="8" t="s">
         <v>5</v>
       </c>
       <c r="S5" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="T5" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="U5" s="8"/>
       <c r="V5" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W5" s="8"/>
       <c r="X5" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="6" spans="1:24">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D6" s="8">
         <v>4</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F6" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="G6" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="G6" s="8" t="s">
-        <v>186</v>
-      </c>
       <c r="H6" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J6" s="8"/>
       <c r="K6" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M6" s="8"/>
       <c r="N6" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P6" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q6" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R6" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="S6" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T6" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="U6" s="8"/>
       <c r="V6" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W6" s="8"/>
       <c r="X6" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="1:24">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D7" s="8">
         <v>15</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J7" s="8"/>
       <c r="K7" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M7" s="8"/>
       <c r="N7" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O7" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P7" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q7" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R7" s="8" t="s">
         <v>5</v>
       </c>
       <c r="S7" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="T7" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="U7" s="8"/>
       <c r="V7" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W7" s="8"/>
       <c r="X7" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8" spans="1:24">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D8" s="8">
         <v>4</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F8" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="G8" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="G8" s="8" t="s">
-        <v>190</v>
-      </c>
       <c r="H8" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J8" s="8"/>
       <c r="K8" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M8" s="8"/>
       <c r="N8" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O8" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P8" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q8" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R8" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="S8" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T8" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="U8" s="8"/>
       <c r="V8" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W8" s="8"/>
       <c r="X8" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:24">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D9" s="8">
         <v>15</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J9" s="8"/>
       <c r="K9" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M9" s="8"/>
       <c r="N9" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O9" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P9" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q9" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R9" s="8" t="s">
         <v>5</v>
       </c>
       <c r="S9" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="T9" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="U9" s="8"/>
       <c r="V9" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W9" s="8"/>
       <c r="X9" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="10" spans="1:24">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D10" s="8">
         <v>4</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F10" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="G10" s="8" t="s">
-        <v>194</v>
-      </c>
       <c r="H10" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J10" s="8"/>
       <c r="K10" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M10" s="8"/>
       <c r="N10" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O10" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P10" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q10" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R10" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="S10" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T10" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="U10" s="8"/>
       <c r="V10" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W10" s="8"/>
       <c r="X10" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:24">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D11" s="8">
         <v>15</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J11" s="8"/>
       <c r="K11" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M11" s="8"/>
       <c r="N11" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O11" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P11" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q11" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R11" s="8" t="s">
         <v>5</v>
       </c>
       <c r="S11" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="T11" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="U11" s="8"/>
       <c r="V11" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W11" s="8"/>
       <c r="X11" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -4085,439 +4082,439 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1">
       <c r="A1" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>199</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="C2" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="D2" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="8" t="s">
         <v>204</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="C3" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="D3" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="F3" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>204</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="C4" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="D4" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="F4" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="D4" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="F4" s="8" t="s">
+      <c r="G4" s="8" t="s">
         <v>209</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="C5" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="D5" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="F5" s="8" t="s">
+      <c r="G5" s="8" t="s">
         <v>209</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B6" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="D6" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="F6" s="8" t="s">
+      <c r="G6" s="8" t="s">
         <v>213</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="C7" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="D7" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="F7" s="8" t="s">
+      <c r="G7" s="8" t="s">
         <v>209</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B8" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="D8" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F8" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="D8" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="F8" s="8" t="s">
+      <c r="G8" s="8" t="s">
         <v>213</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="C9" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="D9" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F9" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="F9" s="8" t="s">
+      <c r="G9" s="8" t="s">
         <v>218</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="C10" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="D10" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F10" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="D10" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="F10" s="8" t="s">
+      <c r="G10" s="8" t="s">
         <v>218</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="C11" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="D11" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="F11" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="F11" s="8" t="s">
+      <c r="G11" s="8" t="s">
         <v>223</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="C12" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="D12" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F12" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="D12" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="F12" s="8" t="s">
+      <c r="G12" s="8" t="s">
         <v>223</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B13" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="D13" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F13" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="D13" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="F13" s="8" t="s">
+      <c r="G13" s="8" t="s">
         <v>227</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="C14" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="D14" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F14" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="D14" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="F14" s="8" t="s">
+      <c r="G14" s="8" t="s">
         <v>223</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B15" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="D15" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F15" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="F15" s="8" t="s">
+      <c r="G15" s="8" t="s">
         <v>231</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="C16" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="D16" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F16" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="D16" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="F16" s="8" t="s">
+      <c r="G16" s="8" t="s">
         <v>223</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B17" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="D17" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F17" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="D17" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="F17" s="8" t="s">
+      <c r="G17" s="8" t="s">
         <v>227</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="B18" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="C18" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="D18" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F18" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="D18" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="F18" s="8" t="s">
+      <c r="G18" s="8" t="s">
         <v>223</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B19" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="D19" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F19" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="D19" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="F19" s="8" t="s">
+      <c r="G19" s="8" t="s">
         <v>227</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>228</v>
       </c>
     </row>
   </sheetData>
@@ -4538,24 +4535,24 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>235</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C2" s="8">
         <v>3</v>
@@ -4584,427 +4581,427 @@
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1">
       <c r="A1" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="6" t="s">
         <v>241</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B2" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="D2" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="E2" s="8" t="s">
         <v>245</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>246</v>
       </c>
       <c r="F2" s="8"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="D3" s="8" t="s">
+      <c r="E3" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>249</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D4" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>251</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>252</v>
       </c>
       <c r="F4" s="8"/>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="D5" s="8" t="s">
+      <c r="E5" s="8" t="s">
         <v>254</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>255</v>
       </c>
       <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="D6" s="8" t="s">
+      <c r="E6" s="8" t="s">
         <v>257</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>258</v>
       </c>
       <c r="F6" s="8"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="D7" s="8" t="s">
+      <c r="E7" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="E7" s="8" t="s">
-        <v>261</v>
-      </c>
       <c r="F7" s="8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="D8" s="8" t="s">
+      <c r="E8" s="8" t="s">
         <v>263</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>264</v>
       </c>
       <c r="F8" s="8"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="D9" s="8" t="s">
+      <c r="E9" s="8" t="s">
         <v>266</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>267</v>
       </c>
       <c r="F9" s="8"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="D10" s="8" t="s">
+      <c r="E10" s="8" t="s">
         <v>269</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>270</v>
       </c>
       <c r="F10" s="8"/>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>271</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="D11" s="8" t="s">
+      <c r="E11" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="E11" s="8" t="s">
-        <v>273</v>
-      </c>
       <c r="F11" s="8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="D12" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="D12" s="8" t="s">
+      <c r="E12" s="8" t="s">
         <v>275</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>276</v>
       </c>
       <c r="F12" s="8"/>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="D13" s="8" t="s">
+      <c r="E13" s="8" t="s">
         <v>278</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>279</v>
       </c>
       <c r="F13" s="8"/>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="D14" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="D14" s="8" t="s">
+      <c r="E14" s="8" t="s">
         <v>281</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>282</v>
       </c>
       <c r="F14" s="8"/>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="D15" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="D15" s="8" t="s">
+      <c r="E15" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="E15" s="8" t="s">
-        <v>285</v>
-      </c>
       <c r="F15" s="8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="D16" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="B16" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="D16" s="8" t="s">
+      <c r="E16" s="8" t="s">
         <v>287</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>288</v>
       </c>
       <c r="F16" s="8"/>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="D17" s="8" t="s">
+      <c r="E17" s="8" t="s">
         <v>290</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>291</v>
       </c>
       <c r="F17" s="8"/>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="D18" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="B18" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="D18" s="8" t="s">
+      <c r="E18" s="8" t="s">
         <v>293</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>294</v>
       </c>
       <c r="F18" s="8"/>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="D19" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="D19" s="8" t="s">
+      <c r="E19" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="E19" s="8" t="s">
-        <v>297</v>
-      </c>
       <c r="F19" s="8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="B20" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="D20" s="8" t="s">
+      <c r="E20" s="8" t="s">
         <v>299</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>300</v>
       </c>
       <c r="F20" s="8"/>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B21" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>244</v>
-      </c>
       <c r="D21" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F21" s="8"/>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B22" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="C22" s="8" t="s">
-        <v>244</v>
-      </c>
       <c r="D22" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="E22" s="8" t="s">
         <v>302</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>303</v>
       </c>
       <c r="F22" s="8"/>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F23" s="8"/>
     </row>

--- a/example/reports/dmz_firewall-review.xlsx
+++ b/example/reports/dmz_firewall-review.xlsx
@@ -70,7 +70,7 @@
     <t>Backup timestamp</t>
   </si>
   <si>
-    <t>2026-08-07 16:09</t>
+    <t>2026-08-26 23:14</t>
   </si>
   <si>
     <t>Report generated</t>
@@ -640,7 +640,7 @@
     <t>Past its stated expiry date</t>
   </si>
   <si>
-    <t>The description gives an expiry of 2026-06-13, 55 days ago, but the rule is still active.</t>
+    <t>The description gives an expiry of 2026-06-13, 74 days ago, but the rule is still active.</t>
   </si>
   <si>
     <t>Remove the rule, or extend it with a new change reference.</t>
@@ -697,7 +697,7 @@
     <t>Expires soon</t>
   </si>
   <si>
-    <t>The stated expiry is 2026-08-27, in 20 days.</t>
+    <t>The stated expiry is 2026-08-27, in 1 days.</t>
   </si>
   <si>
     <t>Confirm whether the access is still needed before it lapses.</t>
